--- a/knowledge/episodes/2026-10/ym-reklama-scripts/ym-reklama-istoriya-20261016.xlsx
+++ b/knowledge/episodes/2026-10/ym-reklama-scripts/ym-reklama-istoriya-20261016.xlsx
@@ -551,7 +551,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="75" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Лист 2 Ставки по неделям</t>
@@ -559,11 +559,11 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Ставка буста по 14 товарам по неделям. У многих товаров два уровня с разницей около 5 пунктов (9/14, 6,6/11,6, 5,5/10,6, 5,3/10,2): либо Маркет берёт +5 п.п. за часть заказов, либо ставку переключали. По данным не разделить - вопрос в поддержку или в кабинет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
+          <t>Списанная ставка буста по 14 товарам по неделям. Списанная не равна выставленной: буст идёт по второму аукциону, Маркет списывает столько, сколько нужно против соседа, но не выше потолка. Разброс внутри товара - аукцион. Потолок виден как повторяющийся максимум (KONUX 14%, зеркала 30%, OSOLIS 11,6%). Доказанные ручные изменения - только рост потолка: 5-1 с 8,8% до 14% (16.09) и до 19% (02-03.10), KONUX 1-3 ступенями с 7% до 14% за июль-сентябрь, зеркала до 30% в июле.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Лист 3 Смены ставки</t>
@@ -571,7 +571,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>То же списком: каждая смена ставки отдельной строкой с датами и числом заказов.</t>
+          <t>То же списком: каждое значение списанной ставки отдельной строкой с датами и числом заказов. Смена значения не равна смене ставки руками (см. правило второго аукциона на листе).</t>
         </is>
       </c>
     </row>
@@ -5595,10 +5595,10 @@
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Та же история ставок, но списком: каждая строка - одно значение ставки (округлено до 0,1%), с какого по какой день заказы шли с ней и сколько их было. Читать сверху вниз по товару: видно, как ставку переключали.</t>
+          <t>Та же история ставок, но списком: каждая строка - одно значение ставки (округлено до 0,1%), с какого по какой день заказы шли с ней и сколько их было. Важно: это СПИСАННАЯ ставка, а не выставленная. Буст Маркета работает по правилу второго аукциона: списывается не ваша ставка, а столько, сколько нужно, чтобы обойти соседа, но не больше вашего потолка. Поэтому разброс значений внутри товара - это аукцион, а не ручные смены. Ручное изменение доказано только там, где списание превысило прежний максимум (потолок подняли).</t>
         </is>
       </c>
     </row>
